--- a/panchang-data/Devghar2026.xlsx
+++ b/panchang-data/Devghar2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5400">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16225,6 +16225,9 @@
   </si>
   <si>
     <t>121°05'09.33</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16714,7 +16717,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16800,7 +16803,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16886,7 +16889,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16972,7 +16975,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -17058,7 +17061,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17144,7 +17147,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17230,7 +17233,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17316,7 +17319,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17402,7 +17405,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17488,7 +17491,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17574,7 +17577,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17660,7 +17663,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17746,7 +17749,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17832,7 +17835,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17918,7 +17921,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18004,7 +18007,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18090,7 +18093,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18176,7 +18179,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18262,7 +18265,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18348,7 +18351,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18434,7 +18437,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18520,7 +18523,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18606,7 +18609,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18692,7 +18695,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18778,7 +18781,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18864,7 +18867,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18950,7 +18953,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -19036,7 +19039,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -19122,7 +19125,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19208,7 +19211,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19294,7 +19297,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19380,7 +19383,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19466,7 +19469,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19552,7 +19555,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19638,7 +19641,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19724,7 +19727,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19810,7 +19813,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19896,7 +19899,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19982,7 +19985,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -20068,7 +20071,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20154,7 +20157,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20240,7 +20243,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20326,7 +20329,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20412,7 +20415,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20498,7 +20501,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20584,7 +20587,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20670,7 +20673,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20756,7 +20759,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20842,7 +20845,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20928,7 +20931,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21014,7 +21017,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21100,7 +21103,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21186,7 +21189,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21272,7 +21275,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21358,7 +21361,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21444,7 +21447,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21530,7 +21533,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21616,7 +21619,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21702,7 +21705,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21788,7 +21791,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21874,7 +21877,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21960,7 +21963,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>568</v>
+        <v>1009</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -22046,7 +22049,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -22132,7 +22135,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22218,7 +22221,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22304,7 +22307,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22390,7 +22393,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22476,7 +22479,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22562,7 +22565,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22648,7 +22651,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22734,7 +22737,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22820,7 +22823,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22906,7 +22909,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22992,7 +22995,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -23078,7 +23081,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23164,7 +23167,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23250,7 +23253,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23336,7 +23339,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23422,7 +23425,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23508,7 +23511,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23594,7 +23597,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23680,7 +23683,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23766,7 +23769,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23852,7 +23855,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23938,7 +23941,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24024,7 +24027,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24110,7 +24113,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24196,7 +24199,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24282,7 +24285,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24368,7 +24371,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24454,7 +24457,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24540,7 +24543,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1009</v>
+        <v>1450</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24626,7 +24629,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24712,7 +24715,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24798,7 +24801,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24884,7 +24887,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24970,7 +24973,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -25056,7 +25059,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -25142,7 +25145,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25228,7 +25231,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25314,7 +25317,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25400,7 +25403,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25486,7 +25489,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25572,7 +25575,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25658,7 +25661,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25744,7 +25747,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25830,7 +25833,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25916,7 +25919,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -26002,7 +26005,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -26088,7 +26091,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26174,7 +26177,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26260,7 +26263,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26346,7 +26349,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26432,7 +26435,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26518,7 +26521,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26604,7 +26607,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26690,7 +26693,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26776,7 +26779,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26862,7 +26865,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26948,7 +26951,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27034,7 +27037,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27120,7 +27123,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1874</v>
+        <v>2309</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27206,7 +27209,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1874</v>
+        <v>2309</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27292,7 +27295,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1874</v>
+        <v>2309</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27378,7 +27381,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1874</v>
+        <v>2309</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27464,7 +27467,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1874</v>
+        <v>2309</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27550,7 +27553,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1874</v>
+        <v>2309</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27636,7 +27639,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1874</v>
+        <v>2309</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27722,7 +27725,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1874</v>
+        <v>2309</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27808,7 +27811,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1874</v>
+        <v>2309</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27894,7 +27897,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1874</v>
+        <v>2309</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27980,7 +27983,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1874</v>
+        <v>2309</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -28066,7 +28069,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1874</v>
+        <v>2309</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -28152,7 +28155,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1874</v>
+        <v>2309</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28238,7 +28241,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1874</v>
+        <v>2309</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28324,7 +28327,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1874</v>
+        <v>2309</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28410,7 +28413,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1874</v>
+        <v>5399</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28496,7 +28499,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1874</v>
+        <v>5399</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28582,7 +28585,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1874</v>
+        <v>5399</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28668,7 +28671,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1874</v>
+        <v>5399</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28754,7 +28757,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1874</v>
+        <v>5399</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28840,7 +28843,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1874</v>
+        <v>5399</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28926,7 +28929,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1874</v>
+        <v>5399</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29012,7 +29015,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1874</v>
+        <v>5399</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -29098,7 +29101,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1874</v>
+        <v>5399</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29184,7 +29187,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1874</v>
+        <v>5399</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29270,7 +29273,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1874</v>
+        <v>5399</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29356,7 +29359,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1874</v>
+        <v>5399</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29442,7 +29445,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1874</v>
+        <v>5399</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29528,7 +29531,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1874</v>
+        <v>5399</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29614,7 +29617,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1874</v>
+        <v>5399</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29700,7 +29703,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2309</v>
+        <v>5399</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29786,7 +29789,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2309</v>
+        <v>5399</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29872,7 +29875,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2309</v>
+        <v>5399</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29958,7 +29961,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2309</v>
+        <v>5399</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30044,7 +30047,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2309</v>
+        <v>5399</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30130,7 +30133,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2309</v>
+        <v>5399</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30216,7 +30219,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2309</v>
+        <v>5399</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30302,7 +30305,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2309</v>
+        <v>5399</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30388,7 +30391,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2309</v>
+        <v>5399</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30474,7 +30477,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2309</v>
+        <v>5399</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30560,7 +30563,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2309</v>
+        <v>5399</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30646,7 +30649,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2309</v>
+        <v>5399</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30732,7 +30735,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2309</v>
+        <v>5399</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30818,7 +30821,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2309</v>
+        <v>5399</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30904,7 +30907,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2309</v>
+        <v>5399</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
